--- a/Data/EXCEL/Transfer/salemon/202208/6719-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6719-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5E25651-BC13-47FC-9E30-877DD75F134F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4334F9F-1435-4183-A3D2-DEFB9EB66D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6719-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,23 +1227,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q50"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="7" width="11.25" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="9" width="9.625" customWidth="1"/>
-    <col min="10" max="11" width="10.25" customWidth="1"/>
-    <col min="12" max="12" width="9.625" customWidth="1"/>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
-    <col min="14" max="14" width="9.625" customWidth="1"/>
-    <col min="15" max="16" width="10.25" customWidth="1"/>
-    <col min="17" max="17" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1267,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1301,7 +1306,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1344,7 +1349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1383,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1436,7 +1441,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1489,7 +1494,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1542,7 +1547,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1595,7 +1600,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1648,7 +1653,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1701,7 +1706,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1754,7 +1759,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1807,7 +1812,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1860,7 +1865,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1913,7 +1918,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1966,7 +1971,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2019,7 +2024,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2072,7 +2077,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2125,7 +2130,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2178,7 +2183,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2231,7 +2236,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2284,7 +2289,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2337,7 +2342,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2390,7 +2395,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2443,7 +2448,7 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2496,7 +2501,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2549,7 +2554,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2602,7 +2607,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2655,7 +2660,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2708,7 +2713,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2761,7 +2766,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2814,7 +2819,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2867,7 +2872,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2920,7 +2925,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2973,7 +2978,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3026,7 +3031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3079,7 +3084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3132,7 +3137,7 @@
         <v>-21.1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3185,7 +3190,7 @@
         <v>-23.9</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3238,7 +3243,7 @@
         <v>-27.2</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3291,7 +3296,7 @@
         <v>-29.6</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3344,7 +3349,7 @@
         <v>-32.1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3397,7 +3402,7 @@
         <v>-32.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3450,7 +3455,7 @@
         <v>-31.1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3503,7 +3508,7 @@
         <v>-32.200000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3556,7 +3561,7 @@
         <v>-31.4</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3609,7 +3614,7 @@
         <v>-28.7</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3662,7 +3667,7 @@
         <v>-33</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3715,7 +3720,7 @@
         <v>-35.9</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3768,7 +3773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3836,7 +3841,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>